--- a/data/trans_bre/P12_1_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P12_1_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 9,21</t>
+          <t>-1,46; 9,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 6,59</t>
+          <t>-5,82; 6,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 5,75</t>
+          <t>-3,37; 5,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 7,44</t>
+          <t>-0,67; 7,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 68,8</t>
+          <t>-8,11; 75,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,47; 45,44</t>
+          <t>-28,18; 42,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 68,18</t>
+          <t>-28,26; 63,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 67,79</t>
+          <t>-5,81; 68,61</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,41; 13,99</t>
+          <t>3,66; 14,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,35; 16,9</t>
+          <t>3,97; 17,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 8,79</t>
+          <t>-1,39; 8,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,42; 13,27</t>
+          <t>3,28; 12,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,78; 145,45</t>
+          <t>22,8; 150,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,88; 128,07</t>
+          <t>22,22; 131,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 114,03</t>
+          <t>-11,53; 116,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,28; 129,91</t>
+          <t>20,79; 118,69</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 10,73</t>
+          <t>-3,87; 10,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 14,37</t>
+          <t>2,16; 14,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 16,48</t>
+          <t>2,25; 17,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 20,17</t>
+          <t>2,93; 20,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 63,07</t>
+          <t>-20,32; 63,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,37; 86,79</t>
+          <t>11,13; 94,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,4; 159,14</t>
+          <t>19,03; 184,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,21; 540,11</t>
+          <t>17,72; 480,09</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 7,25</t>
+          <t>-0,69; 7,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 13,47</t>
+          <t>5,41; 13,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 6,6</t>
+          <t>0,41; 6,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 52,27</t>
+          <t>4,66; 48,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 39,18</t>
+          <t>-3,49; 38,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,98; 88,53</t>
+          <t>29,91; 90,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 56,29</t>
+          <t>2,47; 56,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,57; 403,23</t>
+          <t>31,8; 390,31</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 11,4</t>
+          <t>0,73; 12,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,02; 17,69</t>
+          <t>8,13; 17,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 12,59</t>
+          <t>4,05; 12,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 8,5</t>
+          <t>-1,47; 9,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 73,52</t>
+          <t>3,16; 78,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,29; 140,2</t>
+          <t>45,73; 149,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,88; 113,46</t>
+          <t>27,11; 113,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 63,97</t>
+          <t>-7,87; 71,13</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,34; 17,64</t>
+          <t>10,43; 17,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,81; 23,33</t>
+          <t>14,77; 23,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,09; 12,4</t>
+          <t>4,7; 12,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,6; 13,67</t>
+          <t>1,35; 13,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>97,95; 334,9</t>
+          <t>94,74; 343,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>125,59; 439,78</t>
+          <t>135,55; 448,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51,97; 294,64</t>
+          <t>46,09; 311,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,4; 316,41</t>
+          <t>7,09; 282,37</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,57; 7,31</t>
+          <t>3,49; 7,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,09; 12,02</t>
+          <t>7,89; 11,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,66</t>
+          <t>3,08; 6,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,5; 25,39</t>
+          <t>5,38; 24,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,93; 45,19</t>
+          <t>19,42; 46,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,91; 81,26</t>
+          <t>45,61; 79,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,0; 62,25</t>
+          <t>24,84; 62,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>42,18; 209,88</t>
+          <t>40,16; 219,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P12_1_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P12_1_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,42</t>
+          <t>3,88</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 9,98</t>
+          <t>-2,03; 9,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 6,35</t>
+          <t>-5,63; 6,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 5,22</t>
+          <t>-3,08; 6,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 7,56</t>
+          <t>-0,56; 8,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 75,94</t>
+          <t>-12,06; 69,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,18; 42,51</t>
+          <t>-28,39; 44,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,26; 63,45</t>
+          <t>-25,02; 75,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 68,61</t>
+          <t>-3,83; 73,87</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,94</t>
+          <t>8,07</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>67,87%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 14,5</t>
+          <t>3,24; 14,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,97; 17,02</t>
+          <t>4,45; 16,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 8,59</t>
+          <t>-1,53; 8,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 12,18</t>
+          <t>3,78; 13,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,8; 150,83</t>
+          <t>19,42; 156,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,22; 131,48</t>
+          <t>23,43; 132,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 116,11</t>
+          <t>-14,5; 111,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,79; 118,69</t>
+          <t>25,66; 137,59</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,3</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>105,79%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 10,74</t>
+          <t>-3,61; 10,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 14,57</t>
+          <t>1,63; 14,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 17,41</t>
+          <t>2,09; 17,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,93; 20,17</t>
+          <t>-0,72; 10,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,32; 63,14</t>
+          <t>-18,1; 63,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,13; 94,12</t>
+          <t>8,99; 89,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,03; 184,02</t>
+          <t>17,1; 175,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,72; 480,09</t>
+          <t>-4,1; 88,45</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,59</t>
+          <t>5,93</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>162,89%</t>
+          <t>42,37%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 7,22</t>
+          <t>-0,37; 7,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,41; 13,48</t>
+          <t>5,72; 13,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 6,86</t>
+          <t>0,44; 6,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,66; 48,9</t>
+          <t>2,59; 8,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 38,86</t>
+          <t>-1,64; 41,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,91; 90,73</t>
+          <t>31,57; 89,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 56,56</t>
+          <t>3,01; 57,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,8; 390,31</t>
+          <t>16,2; 70,86</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>8,56</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>59,37%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 12,13</t>
+          <t>0,93; 11,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,13; 17,79</t>
+          <t>8,58; 17,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 12,46</t>
+          <t>4,12; 12,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 9,26</t>
+          <t>4,28; 12,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 78,48</t>
+          <t>4,06; 73,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,73; 149,98</t>
+          <t>47,17; 142,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,11; 113,81</t>
+          <t>26,45; 113,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 71,13</t>
+          <t>23,7; 99,51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,94</t>
+          <t>8,0</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>108,34%</t>
+          <t>92,33%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,43; 17,99</t>
+          <t>9,86; 17,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,77; 23,2</t>
+          <t>14,21; 23,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,7; 12,44</t>
+          <t>4,65; 12,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,35; 13,26</t>
+          <t>0,8; 12,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>94,74; 343,03</t>
+          <t>88,88; 328,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>135,55; 448,26</t>
+          <t>119,59; 436,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,09; 311,12</t>
+          <t>41,77; 272,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,09; 282,37</t>
+          <t>2,97; 252,63</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10,93</t>
+          <t>6,09</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>45,63%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,49; 7,42</t>
+          <t>3,56; 7,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,89; 11,99</t>
+          <t>7,87; 11,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,69</t>
+          <t>3,24; 6,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,38; 24,59</t>
+          <t>4,52; 7,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,42; 46,64</t>
+          <t>20,03; 45,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,61; 79,15</t>
+          <t>48,08; 81,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,84; 62,1</t>
+          <t>26,07; 61,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>40,16; 219,72</t>
+          <t>31,65; 63,11</t>
         </is>
       </c>
     </row>
